--- a/Team-Data/2014-15/3-31-2014-15.xlsx
+++ b/Team-Data/2014-15/3-31-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E2" t="n">
         <v>56</v>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>0.747</v>
+        <v>0.757</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
@@ -691,19 +758,19 @@
         <v>26</v>
       </c>
       <c r="N2" t="n">
-        <v>0.384</v>
+        <v>0.385</v>
       </c>
       <c r="O2" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P2" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="R2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="S2" t="n">
         <v>31.8</v>
@@ -715,7 +782,7 @@
         <v>25.6</v>
       </c>
       <c r="V2" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W2" t="n">
         <v>8.9</v>
@@ -727,19 +794,19 @@
         <v>4.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>102.3</v>
+        <v>102.4</v>
       </c>
       <c r="AC2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD2" t="n">
         <v>5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -772,7 +839,7 @@
         <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP2" t="n">
         <v>24</v>
@@ -799,16 +866,16 @@
         <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ2" t="n">
         <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
         <v>18</v>
@@ -930,7 +997,7 @@
         <v>19</v>
       </c>
       <c r="AG3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH3" t="n">
         <v>12</v>
@@ -978,19 +1045,19 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX3" t="n">
         <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB3" t="n">
         <v>13</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4" t="n">
         <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>0.452</v>
+        <v>0.444</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
@@ -1043,10 +1110,10 @@
         <v>37.2</v>
       </c>
       <c r="J4" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L4" t="n">
         <v>6.5</v>
@@ -1055,19 +1122,19 @@
         <v>20.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.326</v>
+        <v>0.324</v>
       </c>
       <c r="O4" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P4" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.749</v>
+        <v>0.748</v>
       </c>
       <c r="R4" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="S4" t="n">
         <v>32.2</v>
@@ -1079,7 +1146,7 @@
         <v>20.7</v>
       </c>
       <c r="V4" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W4" t="n">
         <v>7</v>
@@ -1088,7 +1155,7 @@
         <v>4.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z4" t="n">
         <v>19.6</v>
@@ -1097,25 +1164,25 @@
         <v>20.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.7</v>
+        <v>97.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3</v>
+        <v>-3.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AE4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF4" t="n">
         <v>18</v>
       </c>
-      <c r="AF4" t="n">
-        <v>17</v>
-      </c>
       <c r="AG4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
         <v>19</v>
@@ -1133,7 +1200,7 @@
         <v>20</v>
       </c>
       <c r="AN4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO4" t="n">
         <v>18</v>
@@ -1157,7 +1224,7 @@
         <v>23</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW4" t="n">
         <v>24</v>
@@ -1175,7 +1242,7 @@
         <v>17</v>
       </c>
       <c r="BB4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -1285,13 +1352,13 @@
         <v>-2.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG5" t="n">
         <v>22</v>
@@ -1330,7 +1397,7 @@
         <v>25</v>
       </c>
       <c r="AS5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT5" t="n">
         <v>9</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -1467,16 +1534,16 @@
         <v>2.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH6" t="n">
         <v>7</v>
@@ -1521,7 +1588,7 @@
         <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
         <v>29</v>
@@ -1530,7 +1597,7 @@
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ6" t="n">
         <v>3</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -1670,16 +1737,16 @@
         <v>24</v>
       </c>
       <c r="AK7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
       </c>
       <c r="AM7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO7" t="n">
         <v>6</v>
@@ -1703,7 +1770,7 @@
         <v>12</v>
       </c>
       <c r="AV7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW7" t="n">
         <v>19</v>
@@ -1718,7 +1785,7 @@
         <v>4</v>
       </c>
       <c r="BA7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB7" t="n">
         <v>6</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E8" t="n">
         <v>45</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.616</v>
+        <v>0.608</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
@@ -1771,49 +1838,49 @@
         <v>39.3</v>
       </c>
       <c r="J8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L8" t="n">
         <v>9.1</v>
       </c>
       <c r="M8" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="O8" t="n">
         <v>16.4</v>
       </c>
       <c r="P8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="R8" t="n">
         <v>10.5</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y8" t="n">
         <v>3.9</v>
@@ -1825,13 +1892,13 @@
         <v>21.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.2</v>
+        <v>104.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1843,7 +1910,7 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1876,7 +1943,7 @@
         <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
         <v>23</v>
@@ -1906,7 +1973,7 @@
         <v>3</v>
       </c>
       <c r="BC8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -2013,10 +2080,10 @@
         <v>-3.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF9" t="n">
         <v>24</v>
@@ -2043,7 +2110,7 @@
         <v>13</v>
       </c>
       <c r="AN9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO9" t="n">
         <v>8</v>
@@ -2058,7 +2125,7 @@
         <v>3</v>
       </c>
       <c r="AS9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
         <v>5</v>
@@ -2073,7 +2140,7 @@
         <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY9" t="n">
         <v>29</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -2117,43 +2184,43 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F10" t="n">
         <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>0.392</v>
+        <v>0.384</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J10" t="n">
         <v>86.3</v>
       </c>
       <c r="K10" t="n">
-        <v>0.429</v>
+        <v>0.428</v>
       </c>
       <c r="L10" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="M10" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="N10" t="n">
-        <v>0.338</v>
+        <v>0.337</v>
       </c>
       <c r="O10" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P10" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q10" t="n">
         <v>0.706</v>
@@ -2162,10 +2229,10 @@
         <v>13</v>
       </c>
       <c r="S10" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T10" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="U10" t="n">
         <v>21.4</v>
@@ -2180,22 +2247,22 @@
         <v>4.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,7 +2274,7 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI10" t="n">
         <v>21</v>
@@ -2225,10 +2292,10 @@
         <v>10</v>
       </c>
       <c r="AN10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP10" t="n">
         <v>16</v>
@@ -2246,7 +2313,7 @@
         <v>4</v>
       </c>
       <c r="AU10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV10" t="n">
         <v>6</v>
@@ -2255,10 +2322,10 @@
         <v>16</v>
       </c>
       <c r="AX10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ10" t="n">
         <v>7</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2366,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.824</v>
+        <v>0.822</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
       </c>
       <c r="I11" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="J11" t="n">
         <v>86.7</v>
@@ -2326,25 +2393,25 @@
         <v>10.7</v>
       </c>
       <c r="M11" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="N11" t="n">
         <v>0.397</v>
       </c>
       <c r="O11" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P11" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="R11" t="n">
         <v>10.2</v>
       </c>
       <c r="S11" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="T11" t="n">
         <v>44.6</v>
@@ -2353,31 +2420,31 @@
         <v>27.4</v>
       </c>
       <c r="V11" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W11" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="X11" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Z11" t="n">
         <v>19.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB11" t="n">
         <v>109.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2404,13 +2471,13 @@
         <v>2</v>
       </c>
       <c r="AM11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP11" t="n">
         <v>26</v>
@@ -2419,10 +2486,10 @@
         <v>9</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
@@ -2434,10 +2501,10 @@
         <v>19</v>
       </c>
       <c r="AW11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
         <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>0.671</v>
+        <v>0.676</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J12" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K12" t="n">
         <v>0.441</v>
@@ -2511,16 +2578,16 @@
         <v>33.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O12" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="P12" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.724</v>
+        <v>0.722</v>
       </c>
       <c r="R12" t="n">
         <v>11.8</v>
@@ -2541,25 +2608,25 @@
         <v>9.5</v>
       </c>
       <c r="X12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y12" t="n">
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.2</v>
+        <v>103.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2571,7 +2638,7 @@
         <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
         <v>20</v>
@@ -2589,16 +2656,16 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AP12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR12" t="n">
         <v>6</v>
@@ -2607,7 +2674,7 @@
         <v>21</v>
       </c>
       <c r="AT12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU12" t="n">
         <v>9</v>
@@ -2616,25 +2683,25 @@
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E13" t="n">
         <v>32</v>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>0.432</v>
+        <v>0.438</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
@@ -2693,7 +2760,7 @@
         <v>21.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.347</v>
+        <v>0.344</v>
       </c>
       <c r="O13" t="n">
         <v>16.7</v>
@@ -2702,25 +2769,25 @@
         <v>21.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.762</v>
+        <v>0.761</v>
       </c>
       <c r="R13" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S13" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="T13" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="U13" t="n">
         <v>21.4</v>
       </c>
       <c r="V13" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W13" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="X13" t="n">
         <v>4.5</v>
@@ -2732,28 +2799,28 @@
         <v>21.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.09999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG13" t="n">
         <v>21</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
@@ -2765,25 +2832,25 @@
         <v>23</v>
       </c>
       <c r="AL13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AO13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP13" t="n">
         <v>18</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS13" t="n">
         <v>5</v>
@@ -2792,25 +2859,25 @@
         <v>7</v>
       </c>
       <c r="AU13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW13" t="n">
         <v>28</v>
       </c>
       <c r="AX13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY13" t="n">
         <v>16</v>
       </c>
       <c r="AZ13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E14" t="n">
         <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>0.653</v>
+        <v>0.662</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2872,19 +2939,19 @@
         <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.374</v>
+        <v>0.375</v>
       </c>
       <c r="O14" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="P14" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.71</v>
+        <v>0.708</v>
       </c>
       <c r="R14" t="n">
         <v>9.5</v>
@@ -2905,34 +2972,34 @@
         <v>7.8</v>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y14" t="n">
         <v>3.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AA14" t="n">
         <v>21.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.5</v>
+        <v>106.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
         <v>28</v>
@@ -2956,7 +3023,7 @@
         <v>3</v>
       </c>
       <c r="AO14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AP14" t="n">
         <v>4</v>
@@ -2980,7 +3047,7 @@
         <v>2</v>
       </c>
       <c r="AW14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX14" t="n">
         <v>9</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E15" t="n">
         <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G15" t="n">
-        <v>0.278</v>
+        <v>0.274</v>
       </c>
       <c r="H15" t="n">
         <v>48.7</v>
       </c>
       <c r="I15" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J15" t="n">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L15" t="n">
         <v>6.5</v>
       </c>
       <c r="M15" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N15" t="n">
         <v>0.344</v>
       </c>
       <c r="O15" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
       <c r="R15" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T15" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="U15" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V15" t="n">
         <v>13.2</v>
@@ -3093,19 +3160,19 @@
         <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.6</v>
+        <v>-5.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,16 +3184,16 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ15" t="n">
         <v>7</v>
       </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL15" t="n">
         <v>25</v>
@@ -3135,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="AN15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO15" t="n">
         <v>12</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
         <v>21</v>
@@ -3150,7 +3217,7 @@
         <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT15" t="n">
         <v>11</v>
@@ -3165,16 +3232,16 @@
         <v>21</v>
       </c>
       <c r="AX15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY15" t="n">
         <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB15" t="n">
         <v>17</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3372,7 @@
         <v>13</v>
       </c>
       <c r="AJ16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK16" t="n">
         <v>9</v>
@@ -3320,7 +3387,7 @@
         <v>15</v>
       </c>
       <c r="AO16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP16" t="n">
         <v>15</v>
@@ -3362,7 +3429,7 @@
         <v>18</v>
       </c>
       <c r="BC16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E17" t="n">
         <v>34</v>
       </c>
       <c r="F17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>0.459</v>
+        <v>0.466</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
@@ -3409,43 +3476,43 @@
         <v>35</v>
       </c>
       <c r="J17" t="n">
-        <v>76.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L17" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M17" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="N17" t="n">
         <v>0.341</v>
       </c>
       <c r="O17" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="P17" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="R17" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="S17" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T17" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="U17" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="V17" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W17" t="n">
         <v>8.1</v>
@@ -3454,7 +3521,7 @@
         <v>4.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z17" t="n">
         <v>19.9</v>
@@ -3463,13 +3530,13 @@
         <v>20.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>-2.2</v>
+        <v>-2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL17" t="n">
         <v>20</v>
@@ -3502,13 +3569,13 @@
         <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3523,7 +3590,7 @@
         <v>28</v>
       </c>
       <c r="AV17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AW17" t="n">
         <v>10</v>
@@ -3532,7 +3599,7 @@
         <v>22</v>
       </c>
       <c r="AY17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ17" t="n">
         <v>15</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3672,7 +3739,7 @@
         <v>26</v>
       </c>
       <c r="AK18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL18" t="n">
         <v>23</v>
@@ -3717,13 +3784,13 @@
         <v>14</v>
       </c>
       <c r="AZ18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA18" t="n">
         <v>18</v>
       </c>
       <c r="BB18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC18" t="n">
         <v>15</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3854,7 +3921,7 @@
         <v>13</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -3902,7 +3969,7 @@
         <v>8</v>
       </c>
       <c r="BA19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB19" t="n">
         <v>21</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -3937,67 +4004,67 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E20" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F20" t="n">
         <v>34</v>
       </c>
       <c r="G20" t="n">
-        <v>0.528</v>
+        <v>0.534</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J20" t="n">
-        <v>82.5</v>
+        <v>82.7</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O20" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P20" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.764</v>
+        <v>0.758</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T20" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="U20" t="n">
         <v>22.1</v>
       </c>
       <c r="V20" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W20" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Y20" t="n">
         <v>5.8</v>
@@ -4006,16 +4073,16 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
         <v>14</v>
@@ -4033,10 +4100,10 @@
         <v>11</v>
       </c>
       <c r="AJ20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL20" t="n">
         <v>19</v>
@@ -4051,10 +4118,10 @@
         <v>19</v>
       </c>
       <c r="AP20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
         <v>10</v>
@@ -4063,7 +4130,7 @@
         <v>18</v>
       </c>
       <c r="AT20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU20" t="n">
         <v>10</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4084,7 +4151,7 @@
         <v>6</v>
       </c>
       <c r="BA20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB20" t="n">
         <v>16</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-9.699999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4221,7 +4288,7 @@
         <v>28</v>
       </c>
       <c r="AL21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="n">
         <v>21</v>
@@ -4257,7 +4324,7 @@
         <v>23</v>
       </c>
       <c r="AX21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY21" t="n">
         <v>6</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>2.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>12</v>
@@ -4451,7 +4518,7 @@
         <v>16</v>
       </c>
       <c r="BB22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -4483,34 +4550,34 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E23" t="n">
         <v>22</v>
       </c>
       <c r="F23" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>0.301</v>
+        <v>0.297</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J23" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L23" t="n">
         <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N23" t="n">
         <v>0.35</v>
@@ -4519,22 +4586,22 @@
         <v>14.1</v>
       </c>
       <c r="P23" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
       <c r="R23" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T23" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="U23" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V23" t="n">
         <v>14.9</v>
@@ -4546,22 +4613,22 @@
         <v>3.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
         <v>21.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.09999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6</v>
+        <v>-6.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4576,10 +4643,10 @@
         <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="n">
         <v>12</v>
@@ -4606,7 +4673,7 @@
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
         <v>27</v>
@@ -4615,16 +4682,16 @@
         <v>22</v>
       </c>
       <c r="AV23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX23" t="n">
         <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
         <v>19</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4846,7 @@
         <v>26</v>
       </c>
       <c r="AP24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4995,7 @@
         <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF25" t="n">
         <v>15</v>
@@ -4964,7 +5031,7 @@
         <v>23</v>
       </c>
       <c r="AQ25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR25" t="n">
         <v>13</v>
@@ -4973,7 +5040,7 @@
         <v>14</v>
       </c>
       <c r="AT25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>4.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
         <v>6</v>
@@ -5116,7 +5183,7 @@
         <v>5</v>
       </c>
       <c r="AG26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH26" t="n">
         <v>10</v>
@@ -5167,7 +5234,7 @@
         <v>27</v>
       </c>
       <c r="AX26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5179,7 +5246,7 @@
         <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4</v>
       </c>
       <c r="AD27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5319,7 +5386,7 @@
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -5417,13 +5484,13 @@
         <v>0.463</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="O28" t="n">
         <v>16.9</v>
@@ -5450,34 +5517,34 @@
         <v>13.9</v>
       </c>
       <c r="W28" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA28" t="n">
         <v>19.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.6</v>
+        <v>102.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE28" t="n">
         <v>8</v>
       </c>
       <c r="AF28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG28" t="n">
         <v>7</v>
@@ -5501,13 +5568,13 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO28" t="n">
         <v>14</v>
       </c>
       <c r="AP28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ28" t="n">
         <v>5</v>
@@ -5525,10 +5592,10 @@
         <v>4</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX28" t="n">
         <v>8</v>
@@ -5543,7 +5610,7 @@
         <v>20</v>
       </c>
       <c r="BB28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
@@ -5689,7 +5756,7 @@
         <v>4</v>
       </c>
       <c r="AP29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ29" t="n">
         <v>2</v>
@@ -5713,7 +5780,7 @@
         <v>17</v>
       </c>
       <c r="AX29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY29" t="n">
         <v>19</v>
@@ -5722,7 +5789,7 @@
         <v>17</v>
       </c>
       <c r="BA29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB29" t="n">
         <v>4</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
         <v>18</v>
@@ -5844,7 +5911,7 @@
         <v>19</v>
       </c>
       <c r="AG30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH30" t="n">
         <v>30</v>
@@ -5859,7 +5926,7 @@
         <v>19</v>
       </c>
       <c r="AL30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM30" t="n">
         <v>17</v>
@@ -5871,10 +5938,10 @@
         <v>15</v>
       </c>
       <c r="AP30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR30" t="n">
         <v>4</v>
@@ -5904,7 +5971,7 @@
         <v>11</v>
       </c>
       <c r="BA30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB30" t="n">
         <v>27</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
         <v>13</v>
@@ -6050,13 +6117,13 @@
         <v>9</v>
       </c>
       <c r="AO31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR31" t="n">
         <v>20</v>
@@ -6077,10 +6144,10 @@
         <v>20</v>
       </c>
       <c r="AX31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ31" t="n">
         <v>18</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-31-2014-15</t>
+          <t>2015-03-31</t>
         </is>
       </c>
     </row>
